--- a/escala_limpeza_25_10_2026.xlsx
+++ b/escala_limpeza_25_10_2026.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Sala e copa</t>
+          <t>Lavanderia</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr"/>
@@ -562,7 +562,7 @@
       <c r="C5" s="6" t="inlineStr"/>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Área traseira da casa</t>
+          <t>Garagem</t>
         </is>
       </c>
     </row>
@@ -592,13 +592,13 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Área frontal da casa</t>
+          <t>Sala e copa</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Cozinha</t>
+          <t>Armários cozinha</t>
         </is>
       </c>
     </row>
@@ -624,15 +624,11 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Panos</t>
+          <t>Cozinha</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Armários cozinha</t>
-        </is>
-      </c>
+      <c r="D9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -640,15 +636,15 @@
           <t>AMANDA</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>AUSENTE</t>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Área frontal da casa</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Garagem</t>
+          <t>Área traseira da casa</t>
         </is>
       </c>
     </row>
@@ -660,11 +656,15 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
+          <t>Panos</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
           <t>Cozinha</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
